--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432561.9007532081</v>
+        <v>432562</v>
       </c>
       <c r="R2" t="n">
-        <v>6380740.806295338</v>
+        <v>6380741</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1998-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105806</v>
+        <v>105815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105815</v>
+        <v>105820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105820</v>
+        <v>105848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105848</v>
+        <v>105854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105854</v>
+        <v>105861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105861</v>
+        <v>105865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105865</v>
+        <v>105872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105875</v>
+        <v>105880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105880</v>
+        <v>105888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74437033</v>
       </c>
       <c r="B2" t="n">
-        <v>105888</v>
+        <v>105898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74437033</v>
+        <v>128202005</v>
       </c>
       <c r="B2" t="n">
-        <v>105898</v>
+        <v>109866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221447</v>
+        <v>220228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra vägskälet mot Tunnabo ca 450 m O, norra vägkanten, Sm</t>
+          <t>Gräsrödjan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432562</v>
+        <v>432655</v>
       </c>
       <c r="R2" t="n">
-        <v>6380741</v>
+        <v>6380732</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -736,17 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1998-07-04</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1998-07-04</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D6g 3743. SOM: Gentianella campestris. LEG: Lennart Persson. KOM: 5 ex</t>
+          <t>Enstaka antal på ytterslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -755,28 +762,251 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Örtrik grusvägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74437033</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östra vägskälet mot Tunnabo ca 450 m O, norra vägkanten, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>432562</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6380741</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stengårdshult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1998-07-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1998-07-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D6g 3743. SOM: Gentianella campestris. LEG: Lennart Persson. KOM: 5 ex</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Örtrik grusvägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4812807</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tunnabo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>432594</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6380756</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stengårdshult</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>F-Gis-0264</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-06-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>F-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via F-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 69075-2021 artfynd.xlsx
+++ b/artfynd/A 69075-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128202005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74437033</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4812807</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>